--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -811,685 +811,679 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9943,0.0003,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.9866,0.0000,0.0000,0.0166</t>
-  </si>
-  <si>
-    <t>0.1345,0.0008,0.0003,0.9269</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9920,0.0013,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9724,0.0002,0.0003,0.0299</t>
+  </si>
+  <si>
+    <t>0.0965,0.0029,0.0002,0.9444</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9988,0.0009,0.0000,0.0001</t>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0673,0.0006,0.9248,0.0009</t>
+  </si>
+  <si>
+    <t>0.0180,0.0010,0.9771,0.0011</t>
+  </si>
+  <si>
+    <t>0.0225,0.0007,0.9790,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0035,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.0914,0.0004,0.9247,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9989,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7398,0.0001,0.3798,0.0001</t>
+  </si>
+  <si>
+    <t>0.9819,0.0011,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0018,0.9942,0.0008</t>
+  </si>
+  <si>
+    <t>0.0337,0.0000,0.9750,0.0001</t>
+  </si>
+  <si>
+    <t>0.2280,0.0005,0.8303,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9972,0.0015</t>
+  </si>
+  <si>
+    <t>0.5498,0.4462,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.1501,0.6752,0.0384,0.0014</t>
+  </si>
+  <si>
+    <t>0.0002,0.0024,0.9995,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.9989,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9818,0.0008,0.0198,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0008,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.0651,0.9305,0.0096,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9990,0.0099,0.0000</t>
+  </si>
+  <si>
+    <t>0.0135,0.9687,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.0217,0.0000,0.9662,0.0006</t>
+  </si>
+  <si>
+    <t>0.0061,0.2779,0.9669,0.0006</t>
+  </si>
+  <si>
+    <t>0.0932,0.0000,0.8713,0.0015</t>
+  </si>
+  <si>
+    <t>0.0004,0.0398,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9990,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.6761,0.0001,0.9387</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0062,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0019,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.9973,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.2126,0.9912,0.0007</t>
+  </si>
+  <si>
+    <t>0.9948,0.0042,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9991,0.0036</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9674,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0119,0.9982,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9978,0.0013</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8685,0.0002,0.2388,0.0001</t>
+  </si>
+  <si>
+    <t>0.9815,0.0016,0.0101,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0007,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9493,0.5563,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9866,0.9624,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9958,0.1495,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0116,0.9992</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0045,0.0000,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0028,0.9984</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9931,0.6460,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9916,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9847,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0321,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9957,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9840,0.4903,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9955,0.0071,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0034,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0011</t>
+  </si>
+  <si>
+    <t>0.0040,0.0036,0.9920,0.0003</t>
+  </si>
+  <si>
+    <t>0.0447,0.0018,0.9450,0.0042</t>
+  </si>
+  <si>
+    <t>0.0027,0.0004,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0097,0.9906,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9988,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.8216,0.3163,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.2615,0.0098,0.5578,0.0012</t>
+  </si>
+  <si>
+    <t>0.9696,0.0002,0.0335,0.0000</t>
+  </si>
+  <si>
+    <t>0.1786,0.3692,0.0504,0.0198</t>
+  </si>
+  <si>
+    <t>0.4112,0.0047,0.4452,0.0022</t>
+  </si>
+  <si>
+    <t>0.0003,0.0543,0.0002,0.9976</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0062,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9937,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9989,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.5266,0.4682,0.0065,0.0000</t>
+  </si>
+  <si>
+    <t>0.6859,0.3453,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9768,0.9855,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0067,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0022,0.9956,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9556,0.0005,0.0439,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.0001,0.9933,0.0007</t>
+  </si>
+  <si>
+    <t>0.9762,0.0001,0.0190,0.0001</t>
+  </si>
+  <si>
+    <t>0.0746,0.0002,0.0003,0.9734</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9940,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9959,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.0046,0.9906,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8389,0.0002,0.0016,0.1861</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9984,0.0029</t>
+  </si>
+  <si>
+    <t>0.9954,0.0000,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.0553,0.9486,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.9970,0.0010,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0033,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4972,0.0459,0.2474,0.0001</t>
+  </si>
+  <si>
+    <t>0.9193,0.0568,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9669,0.0094,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.8630,0.1367,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.8976,0.1664,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0384,0.9927,0.0006</t>
+  </si>
+  <si>
+    <t>0.9994,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9857,0.0148,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9848,0.0118,0.0038,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.5094,0.9954,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0192,0.9992,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9972,0.0002</t>
+  </si>
+  <si>
+    <t>0.0479,0.0003,0.9600,0.0002</t>
+  </si>
+  <si>
+    <t>0.0207,0.0010,0.9768,0.0001</t>
+  </si>
+  <si>
+    <t>0.0938,0.0052,0.8916,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.3620,0.9551,0.0004</t>
+  </si>
+  <si>
+    <t>0.8515,0.0023,0.1364,0.0001</t>
+  </si>
+  <si>
+    <t>0.5821,0.0007,0.4543,0.0003</t>
+  </si>
+  <si>
+    <t>0.0269,0.0007,0.9665,0.0059</t>
+  </si>
+  <si>
+    <t>0.3141,0.8581,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.9961,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0017,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7088,0.3910,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0753,0.9287,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.8701,0.0530,0.0079,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9881,0.0007,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.1142,0.0174,0.7673,0.0024</t>
+  </si>
+  <si>
+    <t>0.0416,0.0080,0.9104,0.0077</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9987,0.0013</t>
+  </si>
+  <si>
+    <t>0.0031,0.0081,0.9870,0.0019</t>
+  </si>
+  <si>
+    <t>0.0004,0.2768,0.9944,0.0005</t>
+  </si>
+  <si>
+    <t>0.0084,0.0010,0.9902,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.4415,0.7860,0.0009</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9984,0.0013,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0032,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9999,0.0053</t>
+  </si>
+  <si>
+    <t>0.0084,0.6903,0.2621,0.0022</t>
+  </si>
+  <si>
+    <t>0.9865,0.0020,0.0036,0.0011</t>
+  </si>
+  <si>
+    <t>0.1269,0.0000,0.9441,0.0000</t>
+  </si>
+  <si>
+    <t>0.0365,0.0108,0.9586,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0372,0.9891,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0009,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0013,0.9960,0.0004</t>
+  </si>
+  <si>
+    <t>0.7768,0.0016,0.1050,0.0042</t>
+  </si>
+  <si>
+    <t>0.9948,0.0000,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9863,0.0002,0.0075,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.0014,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.6937,0.0008,0.4367,0.0000</t>
-  </si>
-  <si>
-    <t>0.2288,0.0001,0.8744,0.0000</t>
-  </si>
-  <si>
-    <t>0.9107,0.0002,0.1235,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0124,0.9914,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9791,0.0009,0.0088,0.0001</t>
-  </si>
-  <si>
-    <t>0.9548,0.0021,0.0141,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.0040,0.0013,0.9909,0.0017</t>
-  </si>
-  <si>
-    <t>0.9104,0.0001,0.1256,0.0000</t>
-  </si>
-  <si>
-    <t>0.7650,0.0006,0.3067,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.9987,0.0007</t>
-  </si>
-  <si>
-    <t>0.3934,0.7468,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.2624,0.1685,0.2081,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0040,0.9997,0.0045</t>
-  </si>
-  <si>
-    <t>0.0030,0.9943,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.4306,0.0005,0.6812,0.0006</t>
-  </si>
-  <si>
-    <t>0.0822,0.9170,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.9970,0.0065,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.9706,0.0136,0.0003</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.9918,0.0031</t>
-  </si>
-  <si>
-    <t>0.0214,0.0028,0.9581,0.0017</t>
-  </si>
-  <si>
-    <t>0.0059,0.0002,0.9914,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0145,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.7934,0.0001,0.8291</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0031,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1124,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0075,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0025,0.9968,0.0012</t>
-  </si>
-  <si>
-    <t>0.9977,0.0034,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.9995,0.0066</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9657,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0155,0.9997,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0017,0.9955,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0088,0.9916,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8544,0.0001,0.2589,0.0001</t>
-  </si>
-  <si>
-    <t>0.9870,0.0021,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.0050,0.0008,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9700,0.8394,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9683,0.9935,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.2629,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.7832,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0037,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0049,0.9981</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
+    <t>0.9973,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9901,0.0183,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0018,0.9981,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0102,0.0038,0.9828,0.0002</t>
+  </si>
+  <si>
+    <t>0.6552,0.0001,0.4587,0.0001</t>
+  </si>
+  <si>
+    <t>0.0090,0.0005,0.9793,0.0057</t>
+  </si>
+  <si>
+    <t>0.0204,0.0007,0.9718,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9987,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0000,0.0005,0.0007</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0000,0.9980,0.1767,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9834,0.7516,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.5846,0.9864,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9875,0.7498,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0132,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0064,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0020,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.0044,0.0013,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.9048,0.0002,0.0571,0.0017</t>
-  </si>
-  <si>
-    <t>0.0163,0.0015,0.9886,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.9965,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8452,0.2314,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.6668,0.0153,0.2033,0.0002</t>
-  </si>
-  <si>
-    <t>0.9889,0.0001,0.0099,0.0000</t>
-  </si>
-  <si>
-    <t>0.7391,0.0625,0.0277,0.0053</t>
-  </si>
-  <si>
-    <t>0.9135,0.0075,0.0380,0.0007</t>
-  </si>
-  <si>
-    <t>0.0011,0.0206,0.0071,0.9881</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9979,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.8552,0.1880,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.5173,0.4730,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0021,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9959,0.0005,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9773,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0318,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0087,0.0007,0.9858,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0004,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4532,0.0003,0.6308,0.0001</t>
-  </si>
-  <si>
-    <t>0.1251,0.0001,0.8945,0.0005</t>
-  </si>
-  <si>
-    <t>0.0487,0.0015,0.9261,0.0012</t>
-  </si>
-  <si>
-    <t>0.0357,0.0002,0.0002,0.9895</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0489,0.9390,0.0070,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.3221,0.0000,0.0006,0.8744</t>
-  </si>
-  <si>
-    <t>0.0033,0.0018,0.9920,0.0060</t>
-  </si>
-  <si>
-    <t>0.9846,0.0000,0.0139,0.0004</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.1700,0.8145,0.0090,0.0004</t>
-  </si>
-  <si>
-    <t>0.9921,0.0046,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0020,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0411,0.3891,0.3942,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9645,0.0102,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9771,0.0234,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.6752,0.4583,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0071,0.0122,0.9873,0.0021</t>
-  </si>
-  <si>
-    <t>0.9988,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9839,0.0175,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0011,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9856,0.0086,0.0049,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1659,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0113,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0016,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.0026,0.9966,0.0007</t>
-  </si>
-  <si>
-    <t>0.4656,0.0004,0.5555,0.0005</t>
-  </si>
-  <si>
-    <t>0.0439,0.0009,0.9513,0.0002</t>
-  </si>
-  <si>
-    <t>0.1063,0.0204,0.7868,0.0001</t>
-  </si>
-  <si>
-    <t>0.0062,0.0794,0.9646,0.0002</t>
-  </si>
-  <si>
-    <t>0.1685,0.0030,0.8035,0.0001</t>
-  </si>
-  <si>
-    <t>0.9674,0.0018,0.0143,0.0002</t>
-  </si>
-  <si>
-    <t>0.0025,0.0004,0.9956,0.0006</t>
-  </si>
-  <si>
-    <t>0.0222,0.9869,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.9969,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9215,0.1489,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6083,0.5964,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0389,0.9655,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.8525,0.0294,0.0279,0.0013</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9861,0.0022,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.3919,0.0052,0.4455,0.0030</t>
-  </si>
-  <si>
-    <t>0.0395,0.0080,0.9084,0.0062</t>
-  </si>
-  <si>
-    <t>0.0025,0.0005,0.9951,0.0012</t>
-  </si>
-  <si>
-    <t>0.0063,0.0054,0.9819,0.0007</t>
-  </si>
-  <si>
-    <t>0.0012,0.0252,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.0092,0.0003,0.9877,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0163,0.9858,0.0019</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0033,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0010,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0040,0.9997,0.0024</t>
-  </si>
-  <si>
-    <t>0.0028,0.0210,0.9893,0.0012</t>
-  </si>
-  <si>
-    <t>0.9965,0.0003,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0313,0.0001,0.9817,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0054,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.0138,0.9978,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0428,0.0010,0.9485,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0050,0.9959,0.0008</t>
-  </si>
-  <si>
-    <t>0.8721,0.0016,0.0533,0.0033</t>
-  </si>
-  <si>
-    <t>0.9781,0.0000,0.0203,0.0001</t>
-  </si>
-  <si>
-    <t>0.9783,0.0002,0.0089,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0026,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0068,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0032,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0031,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0185,0.9879,0.0003</t>
-  </si>
-  <si>
-    <t>0.0556,0.0000,0.9598,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0015,0.9935,0.0131</t>
-  </si>
-  <si>
-    <t>0.0080,0.0009,0.9872,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.9919,0.0025</t>
-  </si>
-  <si>
-    <t>0.9849,0.0000,0.0014,0.0039</t>
-  </si>
-  <si>
-    <t>0.0010,0.0012,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0065,0.0000,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9859,0.0004,0.0005,0.0062</t>
+    <t>0.0025,0.0004,0.0009,0.9980</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0000,0.0003</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1911,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1973,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2040,10 +2034,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2051,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2068,10 +2062,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2096,10 +2090,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2121,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2135,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2183,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2191,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2205,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2219,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2236,10 +2230,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2250,10 +2244,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2261,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2278,10 +2272,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2292,10 +2286,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2317,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2331,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2348,10 +2342,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,7 +2359,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2373,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,7 +2387,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2401,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2415,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2429,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2443,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2471,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,7 +2485,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2499,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2513,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2723,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2737,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2793,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2821,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,7 +2835,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2849,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2863,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2877,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,10 +2902,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2919,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2933,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2947,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2961,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2975,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +2989,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,10 +3000,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3017,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3031,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3048,10 +3042,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3059,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,10 +3070,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>273</v>
+        <v>348</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3115,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>273</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3219,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3325,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3342,10 +3336,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3353,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3367,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>285</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3381,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3395,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3409,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>285</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3457,7 +3451,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,10 +3462,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,7 +3479,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,10 +3490,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3504,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3521,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>280</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3577,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3605,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3619,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3661,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3681,7 +3675,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3695,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3723,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>379</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,7 +3745,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,10 +3756,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3787,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,10 +3812,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,10 +3840,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3857,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>389</v>
+        <v>338</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,7 +3913,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3941,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>376</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,7 +3969,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,10 +3994,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,7 +4067,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,10 +4106,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4143,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>352</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>410</v>
+        <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,7 +4305,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4420,10 +4414,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4521,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4535,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4563,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4574,10 +4568,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4599,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4613,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4627,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,10 +4652,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4669,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,10 +4722,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4739,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4941,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,10 +4946,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5005,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5089,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,7 +5103,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5193,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>475</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5271,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,10 +5296,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5313,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5383,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>392</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,7 +5425,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
